--- a/thaco/color/1_Office_color_ DATA.xlsx
+++ b/thaco/color/1_Office_color_ DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AF05A3-851C-ED44-9D8E-303DCF1A0F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7BC08B1-5F2F-414E-B8A1-42095B4F0E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42900" yWindow="2680" windowWidth="33760" windowHeight="18480" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/thaco/color/1_Office_color_ DATA.xlsx
+++ b/thaco/color/1_Office_color_ DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7BC08B1-5F2F-414E-B8A1-42095B4F0E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD6C2D5-8033-5F4D-AEE5-06E0B618AD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42900" yWindow="2680" windowWidth="33760" windowHeight="18480" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45120" yWindow="2120" windowWidth="33760" windowHeight="18480" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="5" r:id="rId1"/>
@@ -5632,9 +5632,7 @@
       <c r="AM2" s="38"/>
       <c r="AN2" s="38"/>
       <c r="AO2" s="38"/>
-      <c r="AP2" s="51">
-        <v>25846153.846153852</v>
-      </c>
+      <c r="AP2" s="51"/>
       <c r="AQ2" s="40">
         <v>60000000</v>
       </c>
@@ -5736,9 +5734,7 @@
       <c r="AM3" s="38"/>
       <c r="AN3" s="38"/>
       <c r="AO3" s="38"/>
-      <c r="AP3" s="51">
-        <v>0</v>
-      </c>
+      <c r="AP3" s="51"/>
       <c r="AQ3" s="40">
         <v>40000000</v>
       </c>
@@ -5842,9 +5838,7 @@
       <c r="AM4" s="38"/>
       <c r="AN4" s="38"/>
       <c r="AO4" s="38"/>
-      <c r="AP4" s="51">
-        <v>25846153.846153852</v>
-      </c>
+      <c r="AP4" s="51"/>
       <c r="AQ4" s="40">
         <v>40000000</v>
       </c>
@@ -5948,9 +5942,7 @@
       <c r="AM5" s="38"/>
       <c r="AN5" s="38"/>
       <c r="AO5" s="38"/>
-      <c r="AP5" s="51">
-        <v>10195307.692307694</v>
-      </c>
+      <c r="AP5" s="51"/>
       <c r="AQ5" s="40">
         <v>23000000</v>
       </c>
@@ -6056,9 +6048,7 @@
       <c r="AM6" s="38"/>
       <c r="AN6" s="38"/>
       <c r="AO6" s="38"/>
-      <c r="AP6" s="51">
-        <v>9977846.153846154</v>
-      </c>
+      <c r="AP6" s="51"/>
       <c r="AQ6" s="40">
         <v>11000000</v>
       </c>
@@ -6164,9 +6154,7 @@
       <c r="AM7" s="38"/>
       <c r="AN7" s="38"/>
       <c r="AO7" s="38"/>
-      <c r="AP7" s="51">
-        <v>10195307.692307694</v>
-      </c>
+      <c r="AP7" s="51"/>
       <c r="AQ7" s="40">
         <v>23000000</v>
       </c>
@@ -6274,9 +6262,7 @@
       <c r="AM8" s="38"/>
       <c r="AN8" s="38"/>
       <c r="AO8" s="38"/>
-      <c r="AP8" s="51">
-        <v>9977846.153846154</v>
-      </c>
+      <c r="AP8" s="51"/>
       <c r="AQ8" s="40">
         <v>17000000</v>
       </c>
